--- a/data/ams_weekly_data/White_Mulberry/ads_report_week17.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week17.xlsx
@@ -4074,19 +4074,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8079</v>
+        <v>3209</v>
       </c>
       <c r="E2" t="n">
-        <v>273.5</v>
+        <v>109</v>
       </c>
       <c r="F2" t="n">
-        <v>859.26</v>
+        <v>341.3097771646626</v>
       </c>
       <c r="G2" t="n">
-        <v>28378.395</v>
+        <v>11272.28507522842</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4107,19 +4107,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8079</v>
+        <v>12949</v>
       </c>
       <c r="E3" t="n">
-        <v>273.5</v>
+        <v>438</v>
       </c>
       <c r="F3" t="n">
-        <v>859.26</v>
+        <v>1377.210222835337</v>
       </c>
       <c r="G3" t="n">
-        <v>28378.395</v>
+        <v>45484.50492477157</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>103.3333333333333</v>
+        <v>103</v>
       </c>
       <c r="E4" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>5.72</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>103.3333333333333</v>
+        <v>103</v>
       </c>
       <c r="E5" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>5.72</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103.3333333333333</v>
+        <v>103</v>
       </c>
       <c r="E6" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>5.72</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week17.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week17.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
